--- a/temp/profesores_2025-12-01.xlsx
+++ b/temp/profesores_2025-12-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\BD3\Project\APi-SQLite\Proyecto-DB3\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BF2D5C-6F92-44ED-893B-47C722ED967D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974FFA3A-97E6-4652-916F-7CD5DF0C43FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profesores" sheetId="1" r:id="rId1"/>
@@ -935,8 +935,8 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="3" max="3" width="25.75" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
     <col min="6" max="6" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -948,13 +948,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -968,13 +968,13 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
         <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>103</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -1008,13 +1008,13 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" t="s">
-        <v>105</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -1028,13 +1028,13 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
         <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" t="s">
-        <v>107</v>
       </c>
       <c r="F5" t="s">
         <v>38</v>
@@ -1048,13 +1048,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
         <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" t="s">
-        <v>72</v>
       </c>
       <c r="F6" t="s">
         <v>73</v>
@@ -1068,13 +1068,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" t="s">
-        <v>110</v>
       </c>
       <c r="F7" t="s">
         <v>173</v>
@@ -1088,13 +1088,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
         <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" t="s">
-        <v>112</v>
       </c>
       <c r="F8" t="s">
         <v>36</v>
@@ -1108,13 +1108,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" t="s">
-        <v>114</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
@@ -1128,13 +1128,13 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
         <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" t="s">
-        <v>79</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
@@ -1148,13 +1148,13 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
         <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" t="s">
-        <v>117</v>
       </c>
       <c r="F11" t="s">
         <v>37</v>
@@ -1168,13 +1168,13 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" t="s">
         <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
       </c>
       <c r="F12" t="s">
         <v>40</v>
@@ -1188,13 +1188,13 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
         <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>121</v>
       </c>
       <c r="F13" t="s">
         <v>48</v>
@@ -1208,13 +1208,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
         <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>51</v>
@@ -1228,13 +1228,13 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" t="s">
         <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>124</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
@@ -1248,13 +1248,13 @@
         <v>31</v>
       </c>
       <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
         <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" t="s">
-        <v>126</v>
       </c>
       <c r="F16" t="s">
         <v>35</v>
@@ -1268,13 +1268,13 @@
         <v>54</v>
       </c>
       <c r="C17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" t="s">
         <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>128</v>
       </c>
       <c r="F17" t="s">
         <v>45</v>
@@ -1288,13 +1288,13 @@
         <v>56</v>
       </c>
       <c r="C18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" t="s">
         <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
       </c>
       <c r="F18" t="s">
         <v>50</v>
@@ -1308,13 +1308,13 @@
         <v>86</v>
       </c>
       <c r="C19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" t="s">
-        <v>131</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -1328,13 +1328,13 @@
         <v>96</v>
       </c>
       <c r="C20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
         <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>133</v>
       </c>
       <c r="F20" t="s">
         <v>44</v>
@@ -1348,13 +1348,13 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
         <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>135</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
@@ -1368,13 +1368,13 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
         <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>100</v>
       </c>
       <c r="F22" t="s">
         <v>49</v>
@@ -1388,13 +1388,13 @@
         <v>59</v>
       </c>
       <c r="C23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
         <v>138</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>140</v>
       </c>
       <c r="F23" t="s">
         <v>172</v>
@@ -1408,13 +1408,13 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" t="s">
         <v>142</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>144</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
@@ -1428,13 +1428,13 @@
         <v>146</v>
       </c>
       <c r="C25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" t="s">
         <v>147</v>
-      </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" t="s">
-        <v>149</v>
       </c>
       <c r="F25" t="s">
         <v>150</v>
@@ -1448,13 +1448,13 @@
         <v>55</v>
       </c>
       <c r="C26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" t="s">
         <v>151</v>
-      </c>
-      <c r="D26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" t="s">
-        <v>153</v>
       </c>
       <c r="F26" t="s">
         <v>154</v>
@@ -1468,13 +1468,13 @@
         <v>155</v>
       </c>
       <c r="C27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" t="s">
         <v>156</v>
-      </c>
-      <c r="D27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" t="s">
-        <v>158</v>
       </c>
       <c r="F27" t="s">
         <v>159</v>
@@ -1488,13 +1488,13 @@
         <v>161</v>
       </c>
       <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" t="s">
         <v>162</v>
-      </c>
-      <c r="D28" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" t="s">
-        <v>164</v>
       </c>
       <c r="F28" t="s">
         <v>165</v>
@@ -1508,13 +1508,13 @@
         <v>167</v>
       </c>
       <c r="C29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
         <v>168</v>
-      </c>
-      <c r="D29" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" t="s">
-        <v>170</v>
       </c>
       <c r="F29" t="s">
         <v>171</v>
